--- a/Template_Daily_Report.xlsx
+++ b/Template_Daily_Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANAN-NB\Desktop\Claude\Cm_app\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANAN-NB\Desktop\Claude\Cm_app\Template\v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B51FAD2-1412-44B8-AFE9-4A869831FF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB27E92-CEBE-4F77-A6BB-AFBA72A10EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15C402BE-9675-4F7F-93C6-CE572345F033}"/>
   </bookViews>
@@ -1393,27 +1393,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1430,6 +1409,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1449,6 +1431,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1509,20 +1509,25 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>33498</xdr:colOff>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2160000" cy="665175"/>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 4">
+        <xdr:cNvPr id="3" name="รูปภาพ 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3B5F109-426E-46E9-A548-C3A659F45A26}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBBF7DD8-6FA1-42EE-8DB5-C1AB47588A0D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1541,41 +1546,18 @@
         <a:srcRect/>
         <a:stretch/>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="33498" y="28575"/>
-          <a:ext cx="2160000" cy="665175"/>
+          <a:off x="28575" y="28575"/>
+          <a:ext cx="2181225" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1584,22 +1566,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:colOff>16566</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
+      <xdr:rowOff>24848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>544560</xdr:colOff>
+      <xdr:colOff>417030</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>154636</xdr:rowOff>
+      <xdr:rowOff>190086</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="รูปภาพ 2">
+        <xdr:cNvPr id="2" name="รูปภาพ 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{457B3F6E-42FC-4FA6-9D78-DC584C7F6DDB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC221DDC-F872-47F9-9324-96C3423D6055}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1615,14 +1597,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22860" y="22861"/>
-          <a:ext cx="2160000" cy="665175"/>
+          <a:off x="16566" y="24848"/>
+          <a:ext cx="2181225" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1639,22 +1620,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>544560</xdr:colOff>
+      <xdr:colOff>428625</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>154636</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="รูปภาพ 1">
+        <xdr:cNvPr id="3" name="รูปภาพ 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF1C8EBA-0BA4-475A-AC7A-F57346E54C6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F959E92E-1B85-4326-A2D7-CC9BB936C779}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1670,14 +1651,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22860" y="22861"/>
-          <a:ext cx="2160000" cy="665175"/>
+          <a:off x="28575" y="28575"/>
+          <a:ext cx="2181225" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1694,22 +1674,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:colOff>20485</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
+      <xdr:rowOff>20484</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>544560</xdr:colOff>
+      <xdr:colOff>419613</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>154636</xdr:rowOff>
+      <xdr:rowOff>183228</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="รูปภาพ 1">
+        <xdr:cNvPr id="3" name="รูปภาพ 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F76B9B4-6A1A-4D11-A25A-019537045404}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD36F96A-D4F2-45FE-9AE5-6BE406954D54}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1725,14 +1705,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22860" y="22861"/>
-          <a:ext cx="2160000" cy="665175"/>
+          <a:off x="20485" y="20484"/>
+          <a:ext cx="2181225" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1749,22 +1728,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>22861</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>544560</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>154636</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="รูปภาพ 1">
+        <xdr:cNvPr id="3" name="รูปภาพ 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67736303-BFF8-4ED0-8F5A-0CC93680DEA0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24B51EA1-154D-4D8F-A305-D29D9BA1B760}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1780,14 +1759,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22860" y="22861"/>
-          <a:ext cx="2160000" cy="665175"/>
+          <a:off x="19050" y="19050"/>
+          <a:ext cx="2181225" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4425,109 +4403,109 @@
       <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:18" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="61"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="76"/>
       <c r="Q3" s="17"/>
       <c r="R3" s="17"/>
     </row>
     <row r="4" spans="1:18" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="63"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="76"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:18" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="63"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="76"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
     </row>
     <row r="6" spans="1:18" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="66"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="78"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A7" s="23"/>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="65" t="s">
+      <c r="D7" s="79"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
-      <c r="L7" s="65"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="65"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
       <c r="O7" s="21"/>
       <c r="P7" s="24"/>
       <c r="Q7" s="17"/>
@@ -4539,44 +4517,44 @@
       <c r="R8" s="17"/>
     </row>
     <row r="9" spans="1:18" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="70"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="62"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="63"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="17"/>
     </row>
     <row r="10" spans="1:18" s="22" customFormat="1" ht="21" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="73"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="66"/>
       <c r="Q10" s="21"/>
       <c r="R10" s="21"/>
     </row>
@@ -5243,40 +5221,40 @@
     </row>
     <row r="42" spans="1:22" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="34"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="77"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="77"/>
-      <c r="M42" s="77"/>
-      <c r="N42" s="77"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="78"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="71"/>
+      <c r="L42" s="71"/>
+      <c r="M42" s="71"/>
+      <c r="N42" s="71"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
     </row>
     <row r="43" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="31"/>
-      <c r="B43" s="75" t="s">
+      <c r="B43" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="75"/>
-      <c r="J43" s="75"/>
-      <c r="L43" s="75" t="s">
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="69"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="69"/>
+      <c r="L43" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="M43" s="75"/>
-      <c r="N43" s="75"/>
-      <c r="O43" s="75"/>
+      <c r="M43" s="69"/>
+      <c r="N43" s="69"/>
+      <c r="O43" s="69"/>
       <c r="P43" s="37"/>
     </row>
     <row r="44" spans="1:22" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5301,22 +5279,22 @@
       <c r="A45" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="74"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="68"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
       <c r="F45" s="45"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
       <c r="K45" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="L45" s="74"/>
-      <c r="M45" s="74"/>
-      <c r="N45" s="74"/>
-      <c r="O45" s="74"/>
+      <c r="L45" s="68"/>
+      <c r="M45" s="68"/>
+      <c r="N45" s="68"/>
+      <c r="O45" s="68"/>
       <c r="P45" s="37"/>
     </row>
     <row r="46" spans="1:22" ht="10.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5378,6 +5356,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A5:P5"/>
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="A9:P10"/>
     <mergeCell ref="I7:N7"/>
     <mergeCell ref="B45:E45"/>
@@ -5390,11 +5373,6 @@
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="L42:P42"/>
     <mergeCell ref="E7:H7"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A5:P5"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="C7:D7"/>
   </mergeCells>
   <conditionalFormatting sqref="G14:G15 J14:K15 G16:K17 H18:L18 I20:I21 L20:L21 G34:K36 G37:I40 G41:K41">
     <cfRule type="expression" dxfId="4" priority="6">
